--- a/import-templates/import-template-contacts.xlsx
+++ b/import-templates/import-template-contacts.xlsx
@@ -146,17 +146,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1" style="3"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1" style="3"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1" style="3"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -172,53 +173,59 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -234,30 +241,35 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -276,30 +288,35 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00142</t>
+          <t xml:space="preserve">0105536000123</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
+          <t xml:space="preserve">GS20260012</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">ผู้จัดการฝ่ายวิศวกรรม</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081-234-5678</t>
-        </is>
-      </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">somchai@thairungruang.co.th</t>
+          <t xml:space="preserve">0812345678</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">somchai@example.co.th</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ติดต่อสะดวก จ-ศ ช่วงบ่าย</t>
         </is>
@@ -318,58 +335,64 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00187</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">บริษัท เอ็นเนอร์ยี่ พลัส จำกัด</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0105551000456</t>
+        </is>
+      </c>
+      <c r="D3" s="9"/>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">ห้างหุ้นส่วนจำกัด เอ็นเนอร์ยี่ พลัส</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">เจ้าหน้าที่จัดซื้อ</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">089-876-5432</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">waraporn@energyplus.co.th</t>
-        </is>
-      </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waraporn@example.co.th</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">จับคู่ด้วย tax_id เพราะไม่มีรหัสลูกค้า</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ณัฐพงษ์</t>
+          <t xml:space="preserve">คุณโก้</t>
         </is>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">โรงแรมสุขสบาย ระยอง</t>
-        </is>
-      </c>
+      <c r="D4" s="9"/>
       <c r="E4" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">บริษัท สุขสบาย เซอร์วิส จำกัด</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">หัวหน้าช่างอาคาร</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">038-111-333</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่มีนามสกุลในข้อมูลเดิม</t>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0818772323</t>
+        </is>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไม่มีนามสกุลในข้อมูลเดิม — จับคู่ด้วยชื่อบริษัท</t>
         </is>
       </c>
     </row>
@@ -387,7 +410,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -429,100 +452,80 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ต้องนำเข้าลูกค้า (companies) ให้เสร็จก่อน — ผู้ติดต่อผูกกับบริษัทด้วย customer_code</t>
+          <t xml:space="preserve">ต้องนำเข้าลูกค้า (companies) ให้เสร็จก่อน — ผู้ติดต่อผูกกับบริษัทด้วยรหัสของลูกค้า</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">จับคู่บริษัทจาก customer_code ก่อน ถ้าเว้นว่างจึงใช้ company_name</t>
+          <t xml:space="preserve">ลำดับการจับคู่บริษัท: customer_code → tax_id → company_name (อันไหนกรอกก่อนใช้อันนั้น)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อ-นามสกุลแยกกันคนละช่อง (first_name / last_name) เพราะระบบเก็บแยกกัน</t>
+          <t xml:space="preserve">ลูกค้าเดิมในระบบส่วนใหญ่ไม่มี customer_code แต่มี tax_id — ถ้าผูกกับลูกค้าเดิม แนะนำให้ใช้ tax_id</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">ชื่อ-นามสกุลแยกกันคนละช่อง (first_name / last_name) เพราะระบบเก็บแยกกัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">ผู้ติดต่อ 1 คนผูกได้ 1 บริษัทผ่านเทมเพลตนี้ — ถ้าคนเดียวดูแลหลายบริษัท ให้ผูกบริษัทเพิ่มในแอปทีหลัง</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11"/>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คอลัมน์</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชื่อหัวคอลัมน์</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">จำเป็น</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชนิดข้อมูล</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คำอธิบาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">first_name</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ใช่</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ข้อความ</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ชื่อจริง — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">last_name</t>
+          <t xml:space="preserve">first_name</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -532,24 +535,24 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">นามสกุล</t>
+          <t xml:space="preserve">ชื่อจริง — ถ้าเว้นว่างแถวนั้นจะถูกข้าม</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">last_name</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">แนะนำ</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -559,24 +562,24 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">รหัสลูกค้าของบริษัทที่สังกัด (ตรงกับ customer_code ในเทมเพลตลูกค้า) — วิธีจับคู่ที่แม่นที่สุด</t>
+          <t xml:space="preserve">นามสกุล</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_name</t>
+          <t xml:space="preserve">tax_id</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -586,19 +589,19 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อบริษัทที่สังกัด — ใช้จับคู่เมื่อไม่ได้ใส่ customer_code ต้องสะกดตรงกับที่มีในระบบ</t>
+          <t xml:space="preserve">เลขผู้เสียภาษีของบริษัทที่สังกัด — วิธีจับคู่ที่ครอบคลุมที่สุดสำหรับลูกค้าเดิม (26 จาก 31 รายมีเลขนี้)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -613,19 +616,19 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตำแหน่งงาน เช่น ผู้จัดการฝ่ายวิศวกรรม</t>
+          <t xml:space="preserve">รหัสลูกค้าของบริษัทที่สังกัด — ถ้ากรอกจะใช้จับคู่ก่อน tax_id</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">company_name</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -640,19 +643,19 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">เบอร์โทร — ตั้งรูปแบบช่องเป็น Text ไว้แล้ว เลข 0 นำหน้าจะไม่หาย</t>
+          <t xml:space="preserve">ชื่อบริษัทที่สังกัด — ใช้จับคู่เมื่อไม่ได้ใส่ทั้ง customer_code และ tax_id ต้องสะกดตรงกับที่มีในระบบเป๊ะๆ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">F</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -662,37 +665,91 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">อีเมล</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">อีเมล</t>
+          <t xml:space="preserve">ตำแหน่งงาน เช่น ผู้จัดการฝ่ายวิศวกรรม</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ข้อความ</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">เบอร์โทร — ตั้งรูปแบบช่องเป็น Text ไว้แล้ว เลข 0 นำหน้าจะไม่หาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">อีเมล</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">อีเมล</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุ เช่น ช่วงเวลาที่ติดต่อสะดวก</t>
         </is>
